--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA50"/>
+  <dimension ref="A1:BA48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,16 +671,16 @@
         <v>0.2463706233988044</v>
       </c>
       <c r="J2" t="n">
-        <v>309</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>402</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N2" t="n">
         <v>1022</v>
@@ -752,13 +752,13 @@
         <v>1.081818181818182</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6791208791208792</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9436619718309859</v>
+        <v>0.01173708920187793</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.628272251308901</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>1.168905950095969</v>
@@ -801,16 +801,16 @@
         <v>0.2463706233988044</v>
       </c>
       <c r="J3" t="n">
-        <v>8.131578947368421</v>
+        <v>0.3421052631578947</v>
       </c>
       <c r="K3" t="n">
-        <v>10.57894736842105</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="L3" t="n">
-        <v>8.184210526315789</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>12.60526315789474</v>
+        <v>12.63157894736842</v>
       </c>
       <c r="N3" t="n">
         <v>26.89473684210526</v>
@@ -882,13 +882,13 @@
         <v>1.081818181818182</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6791208791208792</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9436619718309859</v>
+        <v>0.01173708920187793</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.628272251308901</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>1.168905950095969</v>
@@ -931,13 +931,13 @@
         <v>0.2729933110367893</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>399</v>
+        <v>14</v>
       </c>
       <c r="L4" t="n">
-        <v>329</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
         <v>398</v>
@@ -1012,13 +1012,13 @@
         <v>0.9636963696369637</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6583493282149712</v>
+        <v>0.01535508637236084</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.731578947368421</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
         <v>1.384615384615385</v>
@@ -1061,13 +1061,13 @@
         <v>0.2729933110367893</v>
       </c>
       <c r="J5" t="n">
-        <v>9.026315789473685</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="K5" t="n">
-        <v>10.5</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="L5" t="n">
-        <v>8.657894736842104</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="M5" t="n">
         <v>10.47368421052632</v>
@@ -1142,13 +1142,13 @@
         <v>0.9636963696369637</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.6583493282149713</v>
+        <v>0.01535508637236084</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9193548387096775</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.731578947368421</v>
+        <v>2</v>
       </c>
       <c r="AN5" t="n">
         <v>1.384615384615385</v>
@@ -1489,13 +1489,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>29</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>523:10</t>
+          <t>263:01</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>2.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.08</v>
+        <v>0.158</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.045</v>
+        <v>0.09</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.058</v>
+        <v>0.115</v>
       </c>
       <c r="BA8" t="n">
         <v>0.014</v>
@@ -1651,16 +1651,16 @@
         <v>70</v>
       </c>
       <c r="U9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>22</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>519:02</t>
+          <t>269:49</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>4.727</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.058</v>
+        <v>0.112</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.034</v>
+        <v>0.066</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.08</v>
+        <v>0.154</v>
       </c>
       <c r="BA9" t="n">
         <v>0.007</v>
@@ -1816,16 +1816,16 @@
         <v>644</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>188</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1922:42</t>
+          <t>942:08</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>6.604</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.139</v>
+        <v>0.283</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.015</v>
+        <v>0.031</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.052</v>
+        <v>0.106</v>
       </c>
       <c r="BA10" t="n">
         <v>0.224</v>
@@ -1981,16 +1981,16 @@
         <v>37</v>
       </c>
       <c r="U11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>3</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>198:56</t>
+          <t>88:57</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,13 +2070,13 @@
         <v>7.333</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.103</v>
+        <v>0.23</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.012</v>
+        <v>0.027</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.011</v>
+        <v>0.025</v>
       </c>
       <c r="BA11" t="n">
         <v>0.007</v>
@@ -2146,16 +2146,16 @@
         <v>314</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>34</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1365:00</t>
+          <t>684:32</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,13 +2235,13 @@
         <v>5.325</v>
       </c>
       <c r="AX12" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AY12" t="n">
         <v>0.074</v>
       </c>
-      <c r="AY12" t="n">
-        <v>0.037</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>0.104</v>
+        <v>0.208</v>
       </c>
       <c r="BA12" t="n">
         <v>0.049</v>
@@ -2311,16 +2311,16 @@
         <v>594</v>
       </c>
       <c r="U13" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>251</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1711:02</t>
+          <t>851:28</t>
         </is>
       </c>
       <c r="AO13" t="n">
@@ -2400,13 +2400,13 @@
         <v>6.085</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.162</v>
+        <v>0.326</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.026</v>
+        <v>0.053</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.063</v>
+        <v>0.126</v>
       </c>
       <c r="BA13" t="n">
         <v>0.08</v>
@@ -2482,10 +2482,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>51:48</t>
+          <t>41:47</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2565,13 +2565,13 @@
         <v>9</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.179</v>
+        <v>0.222</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.023</v>
+        <v>0.028</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.043</v>
+        <v>0.054</v>
       </c>
       <c r="BA14" t="n">
         <v>0.001</v>
@@ -2641,16 +2641,16 @@
         <v>123</v>
       </c>
       <c r="U15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>46</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>687:48</t>
+          <t>327:53</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>10.727</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.092</v>
+        <v>0.193</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.034</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.042</v>
+        <v>0.089</v>
       </c>
       <c r="BA15" t="n">
         <v>0.008</v>
@@ -2806,16 +2806,16 @@
         <v>139</v>
       </c>
       <c r="U16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>46</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>381:23</t>
+          <t>221:26</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,13 +2895,13 @@
         <v>4.857</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.137</v>
+        <v>0.236</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.016</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.044</v>
+        <v>0.076</v>
       </c>
       <c r="BA16" t="n">
         <v>0.027</v>
@@ -2971,16 +2971,16 @@
         <v>302</v>
       </c>
       <c r="U17" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>60</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>1709:38</t>
+          <t>859:00</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>7.652</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.104</v>
+        <v>0.206</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.015</v>
+        <v>0.029</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.059</v>
+        <v>0.117</v>
       </c>
       <c r="BA17" t="n">
         <v>0.047</v>
@@ -3136,16 +3136,16 @@
         <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>22</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>677:06</t>
+          <t>307:30</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,13 +3225,13 @@
         <v>6</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.053</v>
+        <v>0.116</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.01</v>
+        <v>0.023</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.055</v>
+        <v>0.12</v>
       </c>
       <c r="BA18" t="n">
         <v>0.008</v>
@@ -3301,16 +3301,16 @@
         <v>173</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>57</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>1039:40</t>
+          <t>589:35</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>7.7</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.079</v>
+        <v>0.14</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.039</v>
+        <v>0.068</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="BA19" t="n">
         <v>0.021</v>
@@ -3454,7 +3454,7 @@
         <v>57</v>
       </c>
       <c r="Q20" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R20" t="n">
         <v>62</v>
@@ -3466,16 +3466,16 @@
         <v>291</v>
       </c>
       <c r="U20" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>94</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>1595:26</t>
+          <t>753:40</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -3555,13 +3555,13 @@
         <v>5.158</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.089</v>
+        <v>0.189</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.025</v>
+        <v>0.053</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.039</v>
+        <v>0.082</v>
       </c>
       <c r="BA20" t="n">
         <v>0.082</v>
@@ -3631,10 +3631,10 @@
         <v>59</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>196:51</t>
+          <t>105:49</t>
         </is>
       </c>
       <c r="AO21" t="n">
@@ -3720,13 +3720,13 @@
         <v>3.182</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.119</v>
+        <v>0.222</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.042</v>
+        <v>0.078</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.068</v>
+        <v>0.127</v>
       </c>
       <c r="BA21" t="n">
         <v>0.003</v>
@@ -3796,7 +3796,7 @@
         <v>23</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>96:11</t>
+          <t>56:22</t>
         </is>
       </c>
       <c r="AO22" t="n">
@@ -3885,13 +3885,13 @@
         <v>3.8</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.101</v>
+        <v>0.173</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="BA22" t="n">
         <v>0.007</v>
@@ -3961,16 +3961,16 @@
         <v>346</v>
       </c>
       <c r="U23" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>61</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1218:30</t>
+          <t>629:30</t>
         </is>
       </c>
       <c r="AO23" t="n">
@@ -4050,13 +4050,13 @@
         <v>12.056</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.169</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.028</v>
+        <v>0.055</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.074</v>
+        <v>0.144</v>
       </c>
       <c r="BA23" t="n">
         <v>0.031</v>
@@ -4126,16 +4126,16 @@
         <v>185</v>
       </c>
       <c r="U24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>69</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1307:47</t>
+          <t>607:33</t>
         </is>
       </c>
       <c r="AO24" t="n">
@@ -4215,13 +4215,13 @@
         <v>2.487</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.052</v>
+        <v>0.111</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.047</v>
+        <v>0.101</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.077</v>
+        <v>0.166</v>
       </c>
       <c r="BA24" t="n">
         <v>0.017</v>
@@ -4395,71 +4395,71 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>38</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>3114</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>923</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>521</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>762</v>
       </c>
       <c r="T26" t="n">
-        <v>125</v>
+        <v>3565</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4468,90 +4468,90 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1022</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1242</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>0.823</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>543</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>0.403</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>871</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>7600:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>25</v>
+        <v>3179.8</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>0.542</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>0.979</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.169</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>4.495</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>5.664</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="BA26" t="n">
         <v>0</v>
@@ -4560,44 +4560,44 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>38</v>
       </c>
       <c r="C27" t="n">
-        <v>3114</v>
+        <v>3061</v>
       </c>
       <c r="D27" t="n">
-        <v>733</v>
+        <v>766</v>
       </c>
       <c r="E27" t="n">
-        <v>1352</v>
+        <v>1483</v>
       </c>
       <c r="F27" t="n">
-        <v>357</v>
+        <v>292</v>
       </c>
       <c r="G27" t="n">
-        <v>990</v>
+        <v>909</v>
       </c>
       <c r="H27" t="n">
-        <v>577</v>
+        <v>653</v>
       </c>
       <c r="I27" t="n">
-        <v>720</v>
+        <v>820</v>
       </c>
       <c r="J27" t="n">
-        <v>609</v>
+        <v>630</v>
       </c>
       <c r="K27" t="n">
-        <v>923</v>
+        <v>857</v>
       </c>
       <c r="L27" t="n">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="M27" t="n">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="N27" t="n">
         <v>186</v>
@@ -4606,76 +4606,76 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>521</v>
+        <v>455</v>
       </c>
       <c r="Q27" t="n">
-        <v>479</v>
+        <v>398</v>
       </c>
       <c r="R27" t="n">
-        <v>745</v>
+        <v>690</v>
       </c>
       <c r="S27" t="n">
-        <v>762</v>
+        <v>855</v>
       </c>
       <c r="T27" t="n">
-        <v>3565</v>
+        <v>3626</v>
       </c>
       <c r="U27" t="n">
-        <v>309</v>
+        <v>8</v>
       </c>
       <c r="V27" t="n">
-        <v>402</v>
+        <v>14</v>
       </c>
       <c r="W27" t="n">
-        <v>311</v>
+        <v>6</v>
       </c>
       <c r="X27" t="n">
-        <v>191</v>
+        <v>3</v>
       </c>
       <c r="Y27" t="n">
-        <v>1022</v>
+        <v>1124</v>
       </c>
       <c r="Z27" t="n">
-        <v>1242</v>
+        <v>1376</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.823</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="AB27" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AC27" t="n">
-        <v>543</v>
+        <v>616</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.435</v>
+        <v>0.378</v>
       </c>
       <c r="AE27" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AF27" t="n">
         <v>144</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.361</v>
+        <v>0.431</v>
       </c>
       <c r="AH27" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI27" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.403</v>
+        <v>0.368</v>
       </c>
       <c r="AK27" t="n">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="AL27" t="n">
-        <v>871</v>
+        <v>784</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.355</v>
+        <v>0.314</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
@@ -4683,40 +4683,40 @@
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>3179.8</v>
+        <v>3207.8</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.542</v>
+        <v>0.503</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.586</v>
+        <v>0.556</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.979</v>
+        <v>0.954</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.164</v>
+        <v>0.142</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.246</v>
+        <v>0.273</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.169</v>
+        <v>1.385</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.495</v>
+        <v>5.257</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.664</v>
+        <v>6.642</v>
       </c>
       <c r="AX27" t="n">
         <v>0.2</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.066</v>
+        <v>0.064</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.136</v>
+        <v>0.134</v>
       </c>
       <c r="BA27" t="n">
         <v>0</v>
@@ -4725,1279 +4725,1279 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>38</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3061</v>
-      </c>
-      <c r="D28" t="n">
-        <v>766</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1483</v>
-      </c>
-      <c r="F28" t="n">
-        <v>292</v>
-      </c>
-      <c r="G28" t="n">
-        <v>909</v>
-      </c>
-      <c r="H28" t="n">
-        <v>653</v>
-      </c>
-      <c r="I28" t="n">
-        <v>820</v>
-      </c>
-      <c r="J28" t="n">
-        <v>630</v>
-      </c>
-      <c r="K28" t="n">
-        <v>857</v>
-      </c>
-      <c r="L28" t="n">
-        <v>434</v>
-      </c>
-      <c r="M28" t="n">
-        <v>249</v>
-      </c>
-      <c r="N28" t="n">
-        <v>186</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>455</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>398</v>
-      </c>
-      <c r="R28" t="n">
-        <v>690</v>
-      </c>
-      <c r="S28" t="n">
-        <v>855</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3626</v>
-      </c>
-      <c r="U28" t="n">
-        <v>343</v>
-      </c>
-      <c r="V28" t="n">
-        <v>399</v>
-      </c>
-      <c r="W28" t="n">
-        <v>329</v>
-      </c>
-      <c r="X28" t="n">
-        <v>190</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1124</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1376</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.8169999999999999</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>233</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>616</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>62</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>144</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>125</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>246</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>784</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>7600:00</t>
-        </is>
-      </c>
-      <c r="AO28" t="n">
-        <v>3207.8</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0.954</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>5.257</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>6.642</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr"/>
+          <t>#00 A. BACOT JR. (Per Game)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>32</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="T29" t="n">
+        <v>61</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AO29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0.017</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#00 A. BACOT JR. (Per Game)</t>
+          <t>#1 M. BIRSEN (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>1.938</v>
+        <v>1.781</v>
       </c>
       <c r="D30" t="n">
-        <v>0.531</v>
+        <v>0.312</v>
       </c>
       <c r="E30" t="n">
-        <v>1.219</v>
+        <v>0.75</v>
       </c>
       <c r="F30" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="T30" t="n">
+        <v>70</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK30" t="n">
         <v>0.156</v>
       </c>
-      <c r="G30" t="n">
+      <c r="AL30" t="n">
         <v>0.5</v>
       </c>
-      <c r="H30" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.312</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="T30" t="n">
-        <v>61</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.156</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0.784</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0.406</v>
-      </c>
       <c r="AM30" t="n">
-        <v>0.308</v>
+        <v>0.312</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>2.72</v>
+        <v>1.98</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.445</v>
+        <v>0.466</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.5</v>
+        <v>0.544</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.712</v>
+        <v>0.9</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.287</v>
+        <v>0.174</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.236</v>
+        <v>0.364</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.6</v>
+        <v>0.727</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.8</v>
+        <v>4.727</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.08</v>
+        <v>0.112</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.045</v>
+        <v>0.066</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.058</v>
+        <v>0.154</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.017</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#1 M. BIRSEN (Per Game)</t>
+          <t>#2 W. BALDWIN IV (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C31" t="n">
-        <v>1.781</v>
+        <v>14.081</v>
       </c>
       <c r="D31" t="n">
-        <v>0.312</v>
+        <v>4.054</v>
       </c>
       <c r="E31" t="n">
-        <v>0.75</v>
+        <v>7.649</v>
       </c>
       <c r="F31" t="n">
-        <v>0.219</v>
+        <v>0.865</v>
       </c>
       <c r="G31" t="n">
-        <v>0.625</v>
+        <v>3.108</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5</v>
+        <v>3.378</v>
       </c>
       <c r="I31" t="n">
-        <v>0.594</v>
+        <v>4.243</v>
       </c>
       <c r="J31" t="n">
-        <v>0.25</v>
+        <v>5.486</v>
       </c>
       <c r="K31" t="n">
-        <v>1.156</v>
+        <v>2.405</v>
       </c>
       <c r="L31" t="n">
-        <v>0.469</v>
+        <v>0.676</v>
       </c>
       <c r="M31" t="n">
-        <v>0.25</v>
+        <v>0.649</v>
       </c>
       <c r="N31" t="n">
-        <v>0.094</v>
+        <v>0.649</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.344</v>
+        <v>2.459</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.312</v>
+        <v>2.432</v>
       </c>
       <c r="R31" t="n">
-        <v>1.094</v>
+        <v>1.135</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5620000000000001</v>
+        <v>3.757</v>
       </c>
       <c r="T31" t="n">
-        <v>70</v>
+        <v>644</v>
       </c>
       <c r="U31" t="n">
-        <v>0.344</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0.281</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0.406</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.6879999999999999</v>
+        <v>5.081</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.844</v>
+        <v>5.811</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.874</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.125</v>
+        <v>1.757</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.312</v>
+        <v>3.595</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.4</v>
+        <v>0.489</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>0.595</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.094</v>
+        <v>1.622</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.062</v>
+        <v>0.054</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.125</v>
+        <v>0.189</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.156</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.5</v>
+        <v>2.919</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.312</v>
+        <v>0.278</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>25:27</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>1.98</v>
+        <v>15.083</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.466</v>
+        <v>0.497</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.544</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.9</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.174</v>
+        <v>0.163</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.364</v>
+        <v>0.314</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.727</v>
+        <v>2.231</v>
       </c>
       <c r="AV31" t="n">
-        <v>4</v>
+        <v>4.374</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.727</v>
+        <v>6.604</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.058</v>
+        <v>0.283</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.08</v>
+        <v>0.106</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#2 W. BALDWIN IV (Per Game)</t>
+          <t>#3 S. WILBEKIN (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>6.571</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.571</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="T32" t="n">
         <v>37</v>
       </c>
-      <c r="C32" t="n">
-        <v>14.081</v>
-      </c>
-      <c r="D32" t="n">
-        <v>4.054</v>
-      </c>
-      <c r="E32" t="n">
-        <v>7.649</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3.108</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.378</v>
-      </c>
-      <c r="I32" t="n">
-        <v>4.243</v>
-      </c>
-      <c r="J32" t="n">
-        <v>5.486</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.405</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.459</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.432</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.135</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.757</v>
-      </c>
-      <c r="T32" t="n">
-        <v>644</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.243</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.865</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.865</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.216</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>5.081</v>
+        <v>0.429</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.811</v>
+        <v>0.429</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.874</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.757</v>
+        <v>0.571</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.595</v>
+        <v>1.286</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.489</v>
+        <v>0.444</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.595</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.622</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.367</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.189</v>
+        <v>0.143</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.8110000000000001</v>
+        <v>1.571</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.919</v>
+        <v>3.429</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.278</v>
+        <v>0.458</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>51:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>15.083</v>
+        <v>6.126</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.497</v>
+        <v>0.625</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.624</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.073</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.163</v>
+        <v>0.14</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.314</v>
+        <v>0.028</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.231</v>
+        <v>1.333</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.374</v>
+        <v>6</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.604</v>
+        <v>7.333</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.139</v>
+        <v>0.23</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.015</v>
+        <v>0.027</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.052</v>
+        <v>0.025</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.231</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#3 S. WILBEKIN (Per Game)</t>
+          <t>#4 N. MELLI (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C33" t="n">
-        <v>6.571</v>
+        <v>6.667</v>
       </c>
       <c r="D33" t="n">
-        <v>0.857</v>
+        <v>1.233</v>
       </c>
       <c r="E33" t="n">
-        <v>1.571</v>
+        <v>2.4</v>
       </c>
       <c r="F33" t="n">
-        <v>1.571</v>
+        <v>1.3</v>
       </c>
       <c r="G33" t="n">
-        <v>3.571</v>
+        <v>3.033</v>
       </c>
       <c r="H33" t="n">
-        <v>0.143</v>
+        <v>0.3</v>
       </c>
       <c r="I33" t="n">
-        <v>0.286</v>
+        <v>0.633</v>
       </c>
       <c r="J33" t="n">
-        <v>1.143</v>
+        <v>1.667</v>
       </c>
       <c r="K33" t="n">
-        <v>0.286</v>
+        <v>4.233</v>
       </c>
       <c r="L33" t="n">
-        <v>0.286</v>
+        <v>1.433</v>
       </c>
       <c r="M33" t="n">
-        <v>0.714</v>
+        <v>0.833</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.857</v>
+        <v>1.333</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.857</v>
+        <v>1.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.571</v>
+        <v>2.3</v>
       </c>
       <c r="S33" t="n">
-        <v>1.571</v>
+        <v>1.933</v>
       </c>
       <c r="T33" t="n">
-        <v>37</v>
+        <v>314</v>
       </c>
       <c r="U33" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.429</v>
+        <v>1.133</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.429</v>
+        <v>1.667</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AB33" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>0.571</v>
       </c>
-      <c r="AC33" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
       <c r="AK33" t="n">
-        <v>1.571</v>
+        <v>1.033</v>
       </c>
       <c r="AL33" t="n">
-        <v>3.429</v>
+        <v>2.567</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.458</v>
+        <v>0.403</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>28:25</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.126</v>
+        <v>7.045</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.625</v>
+        <v>0.586</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.624</v>
+        <v>0.584</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.073</v>
+        <v>0.946</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.14</v>
+        <v>0.189</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.028</v>
+        <v>0.055</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.333</v>
+        <v>1.25</v>
       </c>
       <c r="AV33" t="n">
-        <v>6</v>
+        <v>4.075</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.333</v>
+        <v>5.325</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.103</v>
+        <v>0.148</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.012</v>
+        <v>0.074</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.011</v>
+        <v>0.208</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.044</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#4 N. MELLI (Per Game)</t>
+          <t>#8 T. HORTON TUCKER (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C34" t="n">
-        <v>6.667</v>
+        <v>15.944</v>
       </c>
       <c r="D34" t="n">
-        <v>1.233</v>
+        <v>4.694</v>
       </c>
       <c r="E34" t="n">
-        <v>2.4</v>
+        <v>8.222</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3</v>
+        <v>1.056</v>
       </c>
       <c r="G34" t="n">
-        <v>3.033</v>
+        <v>3.667</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3</v>
+        <v>3.389</v>
       </c>
       <c r="I34" t="n">
-        <v>0.633</v>
+        <v>4.444</v>
       </c>
       <c r="J34" t="n">
-        <v>1.667</v>
+        <v>1.972</v>
       </c>
       <c r="K34" t="n">
-        <v>4.233</v>
+        <v>2.667</v>
       </c>
       <c r="L34" t="n">
-        <v>1.433</v>
+        <v>1.056</v>
       </c>
       <c r="M34" t="n">
-        <v>0.833</v>
+        <v>0.806</v>
       </c>
       <c r="N34" t="n">
-        <v>0.5669999999999999</v>
+        <v>1.111</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.333</v>
+        <v>2.278</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="R34" t="n">
-        <v>2.3</v>
+        <v>1.722</v>
       </c>
       <c r="S34" t="n">
-        <v>1.933</v>
+        <v>4.139</v>
       </c>
       <c r="T34" t="n">
-        <v>314</v>
+        <v>594</v>
       </c>
       <c r="U34" t="n">
-        <v>0.233</v>
+        <v>0.111</v>
       </c>
       <c r="V34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.133</v>
+        <v>6.972</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.667</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.68</v>
+        <v>0.787</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.233</v>
+        <v>1.028</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.633</v>
+        <v>2.389</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.368</v>
+        <v>0.43</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.167</v>
+        <v>0.083</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.4</v>
+        <v>0.361</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.417</v>
+        <v>0.231</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.267</v>
+        <v>0.111</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.467</v>
+        <v>0.389</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.571</v>
+        <v>0.286</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.033</v>
+        <v>0.944</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.567</v>
+        <v>3.278</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.403</v>
+        <v>0.288</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>45:30</t>
+          <t>23:39</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>7.045</v>
+        <v>16.122</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.586</v>
+        <v>0.528</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.584</v>
+        <v>0.576</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.946</v>
+        <v>0.989</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.189</v>
+        <v>0.141</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.055</v>
+        <v>0.285</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.25</v>
+        <v>0.866</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.075</v>
+        <v>5.22</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.325</v>
+        <v>6.085</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.074</v>
+        <v>0.326</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.037</v>
+        <v>0.053</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.104</v>
+        <v>0.126</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.064</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#8 T. HORTON TUCKER (Per Game)</t>
+          <t>#10 M. MAHMUTOGLU (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C35" t="n">
-        <v>15.944</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>4.694</v>
+        <v>0.067</v>
       </c>
       <c r="E35" t="n">
-        <v>8.222</v>
+        <v>0.267</v>
       </c>
       <c r="F35" t="n">
-        <v>1.056</v>
+        <v>0.267</v>
       </c>
       <c r="G35" t="n">
-        <v>3.667</v>
+        <v>0.867</v>
       </c>
       <c r="H35" t="n">
-        <v>3.389</v>
+        <v>0.067</v>
       </c>
       <c r="I35" t="n">
-        <v>4.444</v>
+        <v>0.067</v>
       </c>
       <c r="J35" t="n">
-        <v>1.972</v>
+        <v>0.067</v>
       </c>
       <c r="K35" t="n">
-        <v>2.667</v>
+        <v>0.133</v>
       </c>
       <c r="L35" t="n">
-        <v>1.056</v>
+        <v>0.067</v>
       </c>
       <c r="M35" t="n">
-        <v>0.806</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.111</v>
+        <v>0.067</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.278</v>
+        <v>0.133</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.25</v>
+        <v>0.133</v>
       </c>
       <c r="R35" t="n">
-        <v>1.722</v>
+        <v>0.133</v>
       </c>
       <c r="S35" t="n">
-        <v>4.139</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>594</v>
+        <v>4</v>
       </c>
       <c r="U35" t="n">
-        <v>2.222</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.222</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.111</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.389</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.972</v>
+        <v>0.067</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.861000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.787</v>
+        <v>0.333</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.028</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.389</v>
+        <v>0.067</v>
       </c>
       <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="AO35" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AQ35" t="n">
         <v>0.43</v>
       </c>
-      <c r="AE35" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>3.278</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>47:31</t>
-        </is>
-      </c>
-      <c r="AO35" t="n">
-        <v>16.122</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.576</v>
-      </c>
       <c r="AR35" t="n">
-        <v>0.989</v>
+        <v>0.772</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.141</v>
+        <v>0.103</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.285</v>
+        <v>0.059</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.866</v>
+        <v>0.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>5.22</v>
+        <v>8.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.085</v>
+        <v>9</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.162</v>
+        <v>0.222</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.063</v>
+        <v>0.054</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#10 M. MAHMUTOGLU (Per Game)</t>
+          <t>#11 B. BOSTON JR. (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="D36" t="n">
-        <v>0.067</v>
+        <v>1.167</v>
       </c>
       <c r="E36" t="n">
+        <v>2.133</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="J36" t="n">
         <v>0.267</v>
       </c>
-      <c r="F36" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="K36" t="n">
         <v>0.867</v>
       </c>
-      <c r="H36" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.133</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.067</v>
+        <v>0.667</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N36" t="n">
-        <v>0.067</v>
+        <v>0.367</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.133</v>
+        <v>0.367</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.133</v>
+        <v>0.333</v>
       </c>
       <c r="R36" t="n">
-        <v>0.133</v>
+        <v>1.067</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="T36" t="n">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -6006,1321 +6006,1321 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.867</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="AB36" t="n">
         <v>0.2</v>
       </c>
-      <c r="X36" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
       <c r="AC36" t="n">
-        <v>0.067</v>
+        <v>0.767</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>0.261</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.067</v>
+        <v>0.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.067</v>
+        <v>0.167</v>
       </c>
       <c r="AG36" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AH36" t="n">
         <v>0.067</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.067</v>
+        <v>0.267</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.2</v>
+        <v>0.433</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.8</v>
+        <v>1.267</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.25</v>
+        <v>0.342</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>03:27</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>1.296</v>
+        <v>4.415</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.412</v>
+        <v>0.523</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.43</v>
+        <v>0.556</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.772</v>
+        <v>1.019</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.103</v>
+        <v>0.083</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.059</v>
+        <v>0.182</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.5</v>
+        <v>0.727</v>
       </c>
       <c r="AV36" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AW36" t="n">
-        <v>9</v>
+        <v>10.727</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.179</v>
+        <v>0.193</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.023</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.043</v>
+        <v>0.089</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#11 B. BOSTON JR. (Per Game)</t>
+          <t>#12 N. DE COLO (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>4.5</v>
+        <v>10.917</v>
       </c>
       <c r="D37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.583</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>139</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK37" t="n">
         <v>1.167</v>
       </c>
-      <c r="E37" t="n">
-        <v>2.133</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.533</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="T37" t="n">
-        <v>123</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.533</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.867</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.821</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0.433</v>
-      </c>
       <c r="AL37" t="n">
-        <v>1.267</v>
+        <v>2.417</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.342</v>
+        <v>0.483</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>4.415</v>
+        <v>9.127000000000001</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.523</v>
+        <v>0.669</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.556</v>
+        <v>0.74</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.019</v>
+        <v>1.196</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.083</v>
+        <v>0.192</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.182</v>
+        <v>0.432</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.727</v>
+        <v>1.333</v>
       </c>
       <c r="AV37" t="n">
-        <v>10</v>
+        <v>3.524</v>
       </c>
       <c r="AW37" t="n">
-        <v>10.727</v>
+        <v>4.857</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.092</v>
+        <v>0.236</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.034</v>
+        <v>0.016</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.042</v>
+        <v>0.076</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.01</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#12 N. DE COLO (Per Game)</t>
+          <t>#13 T. BIBEROVIC (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C38" t="n">
-        <v>10.917</v>
+        <v>10.667</v>
       </c>
       <c r="D38" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="E38" t="n">
-        <v>3.583</v>
+        <v>3.444</v>
       </c>
       <c r="F38" t="n">
+        <v>2.028</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5.083</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="J38" t="n">
         <v>1.25</v>
       </c>
-      <c r="G38" t="n">
-        <v>2.583</v>
-      </c>
-      <c r="H38" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.333</v>
-      </c>
       <c r="K38" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="L38" t="n">
-        <v>0.25</v>
+        <v>0.583</v>
       </c>
       <c r="M38" t="n">
-        <v>0.25</v>
+        <v>0.389</v>
       </c>
       <c r="N38" t="n">
-        <v>0.25</v>
+        <v>0.306</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.75</v>
+        <v>1.278</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.75</v>
+        <v>1.167</v>
       </c>
       <c r="R38" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T38" t="n">
+        <v>302</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.667</v>
       </c>
-      <c r="S38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>139</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.417</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.083</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>3.833</v>
-      </c>
       <c r="Z38" t="n">
-        <v>4.167</v>
+        <v>1.861</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.92</v>
+        <v>0.896</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.833</v>
+        <v>0.972</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.5</v>
+        <v>1.944</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.556</v>
+        <v>0.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.25</v>
+        <v>0.194</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.583</v>
+        <v>0.722</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.429</v>
+        <v>0.269</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.083</v>
+        <v>0.222</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.167</v>
+        <v>0.528</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.5</v>
+        <v>0.421</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.167</v>
+        <v>1.806</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.417</v>
+        <v>4.556</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.483</v>
+        <v>0.396</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>31:46</t>
+          <t>23:51</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>9.127000000000001</v>
+        <v>10.307</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.669</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.74</v>
+        <v>0.591</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.196</v>
+        <v>1.035</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.192</v>
+        <v>0.124</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.432</v>
+        <v>0.127</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.333</v>
+        <v>0.978</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.524</v>
+        <v>6.674</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.857</v>
+        <v>7.652</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.137</v>
+        <v>0.206</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.029</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.044</v>
+        <v>0.117</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.093</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#13 T. BIBEROVIC (Per Game)</t>
+          <t>#17 O. BITIM (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C39" t="n">
-        <v>10.667</v>
+        <v>2.655</v>
       </c>
       <c r="D39" t="n">
-        <v>1.75</v>
+        <v>0.586</v>
       </c>
       <c r="E39" t="n">
-        <v>3.444</v>
+        <v>0.862</v>
       </c>
       <c r="F39" t="n">
-        <v>2.028</v>
+        <v>0.414</v>
       </c>
       <c r="G39" t="n">
-        <v>5.083</v>
+        <v>1.138</v>
       </c>
       <c r="H39" t="n">
-        <v>1.083</v>
+        <v>0.241</v>
       </c>
       <c r="I39" t="n">
-        <v>1.139</v>
+        <v>0.448</v>
       </c>
       <c r="J39" t="n">
-        <v>1.25</v>
+        <v>0.276</v>
       </c>
       <c r="K39" t="n">
-        <v>2.5</v>
+        <v>1.138</v>
       </c>
       <c r="L39" t="n">
-        <v>0.583</v>
+        <v>0.207</v>
       </c>
       <c r="M39" t="n">
-        <v>0.389</v>
+        <v>0.379</v>
       </c>
       <c r="N39" t="n">
-        <v>0.306</v>
+        <v>0.276</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.278</v>
+        <v>0.379</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.167</v>
+        <v>0.379</v>
       </c>
       <c r="R39" t="n">
-        <v>1.972</v>
+        <v>1.414</v>
       </c>
       <c r="S39" t="n">
-        <v>0.75</v>
+        <v>0.655</v>
       </c>
       <c r="T39" t="n">
-        <v>302</v>
+        <v>75</v>
       </c>
       <c r="U39" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.472</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.083</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.667</v>
+        <v>0.759</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.861</v>
+        <v>0.793</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.896</v>
+        <v>0.957</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.972</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.944</v>
+        <v>0.276</v>
       </c>
       <c r="AD39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE39" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.421</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.806</v>
+        <v>0.345</v>
       </c>
       <c r="AL39" t="n">
-        <v>4.556</v>
+        <v>1</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.396</v>
+        <v>0.345</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>47:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>10.307</v>
+        <v>2.577</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.603</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.591</v>
+        <v>0.604</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.035</v>
+        <v>1.031</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.124</v>
+        <v>0.147</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.127</v>
+        <v>0.121</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.978</v>
+        <v>0.727</v>
       </c>
       <c r="AV39" t="n">
-        <v>6.674</v>
+        <v>5.273</v>
       </c>
       <c r="AW39" t="n">
-        <v>7.652</v>
+        <v>6</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.104</v>
+        <v>0.116</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.015</v>
+        <v>0.023</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.059</v>
+        <v>0.12</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#17 O. BITIM (Per Game)</t>
+          <t>#18 M. JANTUNEN (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C40" t="n">
-        <v>2.655</v>
+        <v>5.548</v>
       </c>
       <c r="D40" t="n">
-        <v>0.586</v>
+        <v>0.774</v>
       </c>
       <c r="E40" t="n">
-        <v>0.862</v>
+        <v>1.613</v>
       </c>
       <c r="F40" t="n">
-        <v>0.414</v>
+        <v>0.903</v>
       </c>
       <c r="G40" t="n">
-        <v>1.138</v>
+        <v>2.645</v>
       </c>
       <c r="H40" t="n">
-        <v>0.241</v>
+        <v>1.29</v>
       </c>
       <c r="I40" t="n">
-        <v>0.448</v>
+        <v>1.516</v>
       </c>
       <c r="J40" t="n">
-        <v>0.276</v>
+        <v>0.71</v>
       </c>
       <c r="K40" t="n">
-        <v>1.138</v>
+        <v>2.129</v>
       </c>
       <c r="L40" t="n">
-        <v>0.207</v>
+        <v>1.097</v>
       </c>
       <c r="M40" t="n">
-        <v>0.379</v>
+        <v>0.419</v>
       </c>
       <c r="N40" t="n">
-        <v>0.276</v>
+        <v>0.258</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.379</v>
+        <v>0.645</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.379</v>
+        <v>0.645</v>
       </c>
       <c r="R40" t="n">
-        <v>1.414</v>
+        <v>3.097</v>
       </c>
       <c r="S40" t="n">
-        <v>0.655</v>
+        <v>1.968</v>
       </c>
       <c r="T40" t="n">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="U40" t="n">
-        <v>0.483</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0.172</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.345</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.241</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.759</v>
+        <v>1.839</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.793</v>
+        <v>2.323</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.957</v>
+        <v>0.792</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.226</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.276</v>
+        <v>0.484</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.25</v>
+        <v>0.467</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.034</v>
+        <v>0.097</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.138</v>
+        <v>0.29</v>
       </c>
       <c r="AJ40" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AO40" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="AP40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK40" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>23:20</t>
-        </is>
-      </c>
-      <c r="AO40" t="n">
-        <v>2.577</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0.603</v>
-      </c>
       <c r="AQ40" t="n">
-        <v>0.604</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.031</v>
+        <v>0.996</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.147</v>
+        <v>0.116</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.121</v>
+        <v>0.303</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.727</v>
+        <v>1.1</v>
       </c>
       <c r="AV40" t="n">
-        <v>5.273</v>
+        <v>6.6</v>
       </c>
       <c r="AW40" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.053</v>
+        <v>0.14</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.01</v>
+        <v>0.068</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.055</v>
+        <v>0.125</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.01</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#18 M. JANTUNEN (Per Game)</t>
+          <t>#20 D. HALL (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C41" t="n">
-        <v>5.548</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>0.774</v>
+        <v>2.067</v>
       </c>
       <c r="E41" t="n">
-        <v>1.613</v>
+        <v>3.733</v>
       </c>
       <c r="F41" t="n">
-        <v>0.903</v>
+        <v>0.967</v>
       </c>
       <c r="G41" t="n">
-        <v>2.645</v>
+        <v>3.333</v>
       </c>
       <c r="H41" t="n">
-        <v>1.29</v>
+        <v>1.833</v>
       </c>
       <c r="I41" t="n">
-        <v>1.516</v>
+        <v>2.2</v>
       </c>
       <c r="J41" t="n">
-        <v>0.71</v>
+        <v>2.733</v>
       </c>
       <c r="K41" t="n">
-        <v>2.129</v>
+        <v>1.833</v>
       </c>
       <c r="L41" t="n">
-        <v>1.097</v>
+        <v>1.133</v>
       </c>
       <c r="M41" t="n">
-        <v>0.419</v>
+        <v>0.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0.258</v>
+        <v>0.267</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.645</v>
+        <v>1.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.645</v>
+        <v>1.733</v>
       </c>
       <c r="R41" t="n">
-        <v>3.097</v>
+        <v>2.067</v>
       </c>
       <c r="S41" t="n">
-        <v>1.968</v>
+        <v>2.733</v>
       </c>
       <c r="T41" t="n">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="U41" t="n">
-        <v>0.194</v>
+        <v>0.1</v>
       </c>
       <c r="V41" t="n">
-        <v>0.871</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.839</v>
+        <v>3.133</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.323</v>
+        <v>3.767</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.792</v>
+        <v>0.832</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.226</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.484</v>
+        <v>1.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.467</v>
+        <v>0.378</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.097</v>
+        <v>0.3</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.065</v>
+        <v>0.033</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.29</v>
+        <v>0.267</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.222</v>
+        <v>0.125</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.839</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.355</v>
+        <v>3.067</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.356</v>
+        <v>0.304</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>33:32</t>
+          <t>25:07</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>5.57</v>
+        <v>9.935</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.5</v>
+        <v>0.498</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.552</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.996</v>
+        <v>0.892</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.116</v>
+        <v>0.191</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.303</v>
+        <v>0.259</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.1</v>
+        <v>1.439</v>
       </c>
       <c r="AV41" t="n">
-        <v>6.6</v>
+        <v>3.719</v>
       </c>
       <c r="AW41" t="n">
-        <v>7.7</v>
+        <v>5.158</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.079</v>
+        <v>0.189</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.039</v>
+        <v>0.053</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.026</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#20 D. HALL (Per Game)</t>
+          <t>#30 C. SILVA (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C42" t="n">
-        <v>8.867000000000001</v>
+        <v>4.727</v>
       </c>
       <c r="D42" t="n">
-        <v>2.067</v>
+        <v>1.818</v>
       </c>
       <c r="E42" t="n">
-        <v>3.733</v>
+        <v>2.909</v>
       </c>
       <c r="F42" t="n">
-        <v>0.967</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>3.333</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.833</v>
+        <v>1.091</v>
       </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>1.273</v>
       </c>
       <c r="J42" t="n">
-        <v>2.733</v>
+        <v>0.273</v>
       </c>
       <c r="K42" t="n">
-        <v>1.833</v>
+        <v>1.091</v>
       </c>
       <c r="L42" t="n">
-        <v>1.133</v>
+        <v>0.636</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5</v>
+        <v>0.364</v>
       </c>
       <c r="N42" t="n">
-        <v>0.267</v>
+        <v>0.182</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>2.067</v>
+        <v>1.455</v>
       </c>
       <c r="S42" t="n">
-        <v>2.733</v>
+        <v>1.818</v>
       </c>
       <c r="T42" t="n">
-        <v>291</v>
+        <v>59</v>
       </c>
       <c r="U42" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0.433</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.133</v>
+        <v>2.636</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.767</v>
+        <v>3.182</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.832</v>
+        <v>0.829</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.273</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.5</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.378</v>
+        <v>0.333</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.9330000000000001</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>3.067</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>53:10</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>9.935</v>
+        <v>4.469</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.498</v>
+        <v>0.625</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.552</v>
+        <v>0.681</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.892</v>
+        <v>1.058</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.191</v>
+        <v>0.224</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.259</v>
+        <v>0.375</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.439</v>
+        <v>0.273</v>
       </c>
       <c r="AV42" t="n">
-        <v>3.719</v>
+        <v>2.909</v>
       </c>
       <c r="AW42" t="n">
-        <v>5.158</v>
+        <v>3.182</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.089</v>
+        <v>0.222</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.025</v>
+        <v>0.078</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.039</v>
+        <v>0.127</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.107</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#30 C. SILVA (Per Game)</t>
+          <t>#32 A. ZAGARS (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>4.727</v>
+        <v>1.417</v>
       </c>
       <c r="D43" t="n">
-        <v>1.818</v>
+        <v>0.25</v>
       </c>
       <c r="E43" t="n">
-        <v>2.909</v>
+        <v>0.583</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="H43" t="n">
-        <v>1.091</v>
+        <v>0.667</v>
       </c>
       <c r="I43" t="n">
-        <v>1.273</v>
+        <v>0.833</v>
       </c>
       <c r="J43" t="n">
-        <v>0.273</v>
+        <v>0.667</v>
       </c>
       <c r="K43" t="n">
-        <v>1.091</v>
+        <v>0.083</v>
       </c>
       <c r="L43" t="n">
-        <v>0.636</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.364</v>
+        <v>0.25</v>
       </c>
       <c r="N43" t="n">
-        <v>0.182</v>
+        <v>0.083</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="T43" t="n">
+        <v>23</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA43" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>1</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.455</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.818</v>
-      </c>
-      <c r="T43" t="n">
-        <v>59</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.182</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.636</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3.182</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.829</v>
-      </c>
       <c r="AB43" t="n">
-        <v>0.273</v>
+        <v>0.083</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.333</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AL43" t="n">
         <v>0.333</v>
       </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>04:41</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>4.469</v>
+        <v>1.7</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.625</v>
+        <v>0.409</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.681</v>
+        <v>0.552</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.058</v>
+        <v>0.833</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.224</v>
+        <v>0.245</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.375</v>
+        <v>0.727</v>
       </c>
       <c r="AU43" t="n">
-        <v>0.273</v>
+        <v>1.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.909</v>
+        <v>2.2</v>
       </c>
       <c r="AW43" t="n">
-        <v>3.182</v>
+        <v>3.8</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.119</v>
+        <v>0.173</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.068</v>
+        <v>0.02</v>
       </c>
       <c r="BA43" t="n">
-        <v>0.01</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#32 A. ZAGARS (Per Game)</t>
+          <t>#50 B. COLSON (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C44" t="n">
-        <v>1.417</v>
+        <v>7.771</v>
       </c>
       <c r="D44" t="n">
-        <v>0.25</v>
+        <v>1.257</v>
       </c>
       <c r="E44" t="n">
-        <v>0.583</v>
+        <v>2.486</v>
       </c>
       <c r="F44" t="n">
-        <v>0.083</v>
+        <v>1.371</v>
       </c>
       <c r="G44" t="n">
-        <v>0.333</v>
+        <v>2.829</v>
       </c>
       <c r="H44" t="n">
-        <v>0.667</v>
+        <v>1.143</v>
       </c>
       <c r="I44" t="n">
-        <v>0.833</v>
+        <v>1.229</v>
       </c>
       <c r="J44" t="n">
-        <v>0.667</v>
+        <v>0.886</v>
       </c>
       <c r="K44" t="n">
-        <v>0.083</v>
+        <v>2.314</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>0.829</v>
       </c>
       <c r="M44" t="n">
-        <v>0.25</v>
+        <v>0.629</v>
       </c>
       <c r="N44" t="n">
-        <v>0.083</v>
+        <v>0.486</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.417</v>
+        <v>0.514</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.417</v>
+        <v>0.486</v>
       </c>
       <c r="R44" t="n">
-        <v>0.333</v>
+        <v>1.114</v>
       </c>
       <c r="S44" t="n">
-        <v>0.917</v>
+        <v>1.371</v>
       </c>
       <c r="T44" t="n">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="U44" t="n">
-        <v>0.167</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -7332,277 +7332,277 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.833</v>
+        <v>1.743</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.833</v>
+        <v>2.114</v>
       </c>
       <c r="AA44" t="n">
-        <v>1</v>
+        <v>0.824</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.083</v>
+        <v>0.629</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.333</v>
+        <v>1.457</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.25</v>
+        <v>0.431</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.083</v>
+        <v>0.057</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.083</v>
+        <v>0.971</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.333</v>
+        <v>2.114</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.25</v>
+        <v>0.459</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>1.7</v>
+        <v>6.369</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.409</v>
+        <v>0.624</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.552</v>
+        <v>0.664</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.833</v>
+        <v>1.22</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.245</v>
+        <v>0.081</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.727</v>
+        <v>0.215</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.6</v>
+        <v>1.722</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.2</v>
+        <v>10.333</v>
       </c>
       <c r="AW44" t="n">
-        <v>3.8</v>
+        <v>12.056</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.101</v>
+        <v>0.169</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.012</v>
+        <v>0.144</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.024</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#50 B. COLSON (Per Game)</t>
+          <t>#92 K. BIRCH (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C45" t="n">
-        <v>7.771</v>
+        <v>3.5</v>
       </c>
       <c r="D45" t="n">
-        <v>1.257</v>
+        <v>1.263</v>
       </c>
       <c r="E45" t="n">
-        <v>2.486</v>
+        <v>2.079</v>
       </c>
       <c r="F45" t="n">
-        <v>1.371</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>2.829</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.143</v>
+        <v>0.974</v>
       </c>
       <c r="I45" t="n">
-        <v>1.229</v>
+        <v>1.395</v>
       </c>
       <c r="J45" t="n">
-        <v>0.886</v>
+        <v>0.474</v>
       </c>
       <c r="K45" t="n">
-        <v>2.314</v>
+        <v>2.368</v>
       </c>
       <c r="L45" t="n">
-        <v>0.829</v>
+        <v>1.368</v>
       </c>
       <c r="M45" t="n">
-        <v>0.629</v>
+        <v>0.289</v>
       </c>
       <c r="N45" t="n">
-        <v>0.486</v>
+        <v>0.421</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.514</v>
+        <v>1.026</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.486</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>1.114</v>
+        <v>2.658</v>
       </c>
       <c r="S45" t="n">
-        <v>1.371</v>
+        <v>1.368</v>
       </c>
       <c r="T45" t="n">
-        <v>346</v>
+        <v>185</v>
       </c>
       <c r="U45" t="n">
-        <v>1.343</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.114</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0.629</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.743</v>
+        <v>1.816</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.114</v>
+        <v>2.316</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.824</v>
+        <v>0.784</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.629</v>
+        <v>0.395</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.457</v>
+        <v>0.711</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.431</v>
+        <v>0.556</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.057</v>
+        <v>0.026</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.971</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.114</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.459</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>34:48</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>6.369</v>
+        <v>3.719</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.624</v>
+        <v>0.608</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.664</v>
+        <v>0.65</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.22</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.081</v>
+        <v>0.276</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.215</v>
+        <v>0.468</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.722</v>
+        <v>0.462</v>
       </c>
       <c r="AV45" t="n">
-        <v>10.333</v>
+        <v>2.026</v>
       </c>
       <c r="AW45" t="n">
-        <v>12.056</v>
+        <v>2.487</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.111</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.028</v>
+        <v>0.101</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.074</v>
+        <v>0.166</v>
       </c>
       <c r="BA45" t="n">
-        <v>0.034</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#92 K. BIRCH (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>38</v>
       </c>
       <c r="C46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>1.263</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>2.079</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -7611,82 +7611,82 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.974</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1.395</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.474</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2.368</v>
+        <v>1.947</v>
       </c>
       <c r="L46" t="n">
-        <v>1.368</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>0.289</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.026</v>
+        <v>0.658</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.658</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.368</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.263</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.263</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0.184</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.816</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.316</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.784</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.395</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.711</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
         <v>0</v>
@@ -7708,117 +7708,117 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>34:24</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>3.719</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.608</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.9409999999999999</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.276</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.468</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.026</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.487</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.052</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>38</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>81.947</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>19.289</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>35.579</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>9.395</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>26.053</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>15.184</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>18.947</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>16.026</v>
       </c>
       <c r="K47" t="n">
-        <v>1.947</v>
+        <v>24.289</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>11.211</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>5.421</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.895</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.658</v>
+        <v>13.711</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>12.632</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>19.605</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>20.053</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3565</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
@@ -7827,90 +7827,90 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>26.895</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>32.684</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>0.823</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>6.211</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>14.289</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.368</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>3.789</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.263</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>3.132</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.403</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>8.132</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>22.921</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>0</v>
+        <v>83.679</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>0.542</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>0.979</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>1.169</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>4.495</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>5.664</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="BA47" t="n">
         <v>0</v>
@@ -7919,495 +7919,165 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>38</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>80.553</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>20.158</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>39.026</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>7.684</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>23.921</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>17.184</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>21.579</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>16.579</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>22.553</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>11.421</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>6.553</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.895</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>11.974</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>10.474</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>18.158</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="T48" t="n">
-        <v>125</v>
+        <v>3626</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>29.579</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>36.211</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>6.132</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>16.211</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.632</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>3.789</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>0.431</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.211</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>3.289</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>6.474</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>20.632</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>0.314</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>0.658</v>
+        <v>84.416</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>0.954</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>1.385</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>5.257</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>6.642</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>38</v>
-      </c>
-      <c r="C49" t="n">
-        <v>81.947</v>
-      </c>
-      <c r="D49" t="n">
-        <v>19.289</v>
-      </c>
-      <c r="E49" t="n">
-        <v>35.579</v>
-      </c>
-      <c r="F49" t="n">
-        <v>9.395</v>
-      </c>
-      <c r="G49" t="n">
-        <v>26.053</v>
-      </c>
-      <c r="H49" t="n">
-        <v>15.184</v>
-      </c>
-      <c r="I49" t="n">
-        <v>18.947</v>
-      </c>
-      <c r="J49" t="n">
-        <v>16.026</v>
-      </c>
-      <c r="K49" t="n">
-        <v>24.289</v>
-      </c>
-      <c r="L49" t="n">
-        <v>11.211</v>
-      </c>
-      <c r="M49" t="n">
-        <v>5.421</v>
-      </c>
-      <c r="N49" t="n">
-        <v>4.895</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>13.711</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>12.605</v>
-      </c>
-      <c r="R49" t="n">
-        <v>19.605</v>
-      </c>
-      <c r="S49" t="n">
-        <v>20.053</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3565</v>
-      </c>
-      <c r="U49" t="n">
-        <v>8.132</v>
-      </c>
-      <c r="V49" t="n">
-        <v>10.579</v>
-      </c>
-      <c r="W49" t="n">
-        <v>8.183999999999999</v>
-      </c>
-      <c r="X49" t="n">
-        <v>5.026</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>26.895</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>32.684</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>6.211</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>14.289</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.368</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>3.789</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.263</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>3.132</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>8.132</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>22.921</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO49" t="n">
-        <v>83.679</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>1.169</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>4.495</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>5.664</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>38</v>
-      </c>
-      <c r="C50" t="n">
-        <v>80.553</v>
-      </c>
-      <c r="D50" t="n">
-        <v>20.158</v>
-      </c>
-      <c r="E50" t="n">
-        <v>39.026</v>
-      </c>
-      <c r="F50" t="n">
-        <v>7.684</v>
-      </c>
-      <c r="G50" t="n">
-        <v>23.921</v>
-      </c>
-      <c r="H50" t="n">
-        <v>17.184</v>
-      </c>
-      <c r="I50" t="n">
-        <v>21.579</v>
-      </c>
-      <c r="J50" t="n">
-        <v>16.579</v>
-      </c>
-      <c r="K50" t="n">
-        <v>22.553</v>
-      </c>
-      <c r="L50" t="n">
-        <v>11.421</v>
-      </c>
-      <c r="M50" t="n">
-        <v>6.553</v>
-      </c>
-      <c r="N50" t="n">
-        <v>4.895</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>11.974</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>10.474</v>
-      </c>
-      <c r="R50" t="n">
-        <v>18.158</v>
-      </c>
-      <c r="S50" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3626</v>
-      </c>
-      <c r="U50" t="n">
-        <v>9.026</v>
-      </c>
-      <c r="V50" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W50" t="n">
-        <v>8.657999999999999</v>
-      </c>
-      <c r="X50" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>29.579</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>36.211</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.8169999999999999</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>6.132</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>16.211</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.632</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>3.789</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.211</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>3.289</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>6.474</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>20.632</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO50" t="n">
-        <v>84.416</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0.954</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>5.257</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>6.642</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="BA50" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
@@ -671,13 +671,13 @@
         <v>0.2463706233988044</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>325</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>405</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="M2" t="n">
         <v>480</v>
@@ -752,13 +752,13 @@
         <v>1.081818181818182</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.02857142857142857</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01173708920187793</v>
+        <v>0.9507042253521126</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.605</v>
       </c>
       <c r="AN2" t="n">
         <v>1.168905950095969</v>
@@ -801,13 +801,13 @@
         <v>0.2463706233988044</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3421052631578947</v>
+        <v>8.552631578947368</v>
       </c>
       <c r="K3" t="n">
-        <v>0.131578947368421</v>
+        <v>10.6578947368421</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>8.447368421052632</v>
       </c>
       <c r="M3" t="n">
         <v>12.63157894736842</v>
@@ -882,13 +882,13 @@
         <v>1.081818181818182</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02857142857142857</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01173708920187793</v>
+        <v>0.9507042253521125</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.605</v>
       </c>
       <c r="AN3" t="n">
         <v>1.168905950095969</v>
@@ -931,13 +931,13 @@
         <v>0.2729933110367893</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>361</v>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>408</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>344</v>
       </c>
       <c r="M4" t="n">
         <v>398</v>
@@ -1012,13 +1012,13 @@
         <v>0.9636963696369637</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01535508637236084</v>
+        <v>0.6928982725527831</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.9400921658986175</v>
       </c>
       <c r="AM4" t="n">
-        <v>2</v>
+        <v>1.669902912621359</v>
       </c>
       <c r="AN4" t="n">
         <v>1.384615384615385</v>
@@ -1061,13 +1061,13 @@
         <v>0.2729933110367893</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2105263157894737</v>
+        <v>9.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3684210526315789</v>
+        <v>10.73684210526316</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1578947368421053</v>
+        <v>9.052631578947368</v>
       </c>
       <c r="M5" t="n">
         <v>10.47368421052632</v>
@@ -1142,13 +1142,13 @@
         <v>0.9636963696369637</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.01535508637236084</v>
+        <v>0.692898272552783</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.9400921658986175</v>
       </c>
       <c r="AM5" t="n">
-        <v>2</v>
+        <v>1.669902912621359</v>
       </c>
       <c r="AN5" t="n">
         <v>1.384615384615385</v>
@@ -1489,13 +1489,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="n">
         <v>29</v>
@@ -1651,16 +1651,16 @@
         <v>70</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="n">
         <v>22</v>
@@ -1816,16 +1816,16 @@
         <v>644</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y10" t="n">
         <v>188</v>
@@ -1981,16 +1981,16 @@
         <v>37</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
         <v>3</v>
@@ -2146,16 +2146,16 @@
         <v>314</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="n">
         <v>34</v>
@@ -2311,16 +2311,16 @@
         <v>594</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="Y13" t="n">
         <v>251</v>
@@ -2482,10 +2482,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>1</v>
@@ -2641,16 +2641,16 @@
         <v>123</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="n">
         <v>46</v>
@@ -2806,16 +2806,16 @@
         <v>139</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="n">
         <v>46</v>
@@ -2971,16 +2971,16 @@
         <v>302</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
         <v>60</v>
@@ -3136,16 +3136,16 @@
         <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y18" t="n">
         <v>22</v>
@@ -3301,16 +3301,16 @@
         <v>173</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y19" t="n">
         <v>57</v>
@@ -3466,16 +3466,16 @@
         <v>291</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y20" t="n">
         <v>94</v>
@@ -3631,10 +3631,10 @@
         <v>59</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>23</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3961,16 +3961,16 @@
         <v>346</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="n">
         <v>61</v>
@@ -4126,16 +4126,16 @@
         <v>185</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y24" t="n">
         <v>69</v>
@@ -4456,16 +4456,16 @@
         <v>3565</v>
       </c>
       <c r="U26" t="n">
-        <v>13</v>
+        <v>325</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>405</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y26" t="n">
         <v>1022</v>
@@ -4621,16 +4621,16 @@
         <v>3626</v>
       </c>
       <c r="U27" t="n">
-        <v>8</v>
+        <v>361</v>
       </c>
       <c r="V27" t="n">
-        <v>14</v>
+        <v>408</v>
       </c>
       <c r="W27" t="n">
-        <v>6</v>
+        <v>344</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>206</v>
       </c>
       <c r="Y27" t="n">
         <v>1124</v>
@@ -4848,13 +4848,13 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="Y29" t="n">
         <v>0.906</v>
@@ -5010,16 +5010,16 @@
         <v>70</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="Y30" t="n">
         <v>0.6879999999999999</v>
@@ -5175,16 +5175,16 @@
         <v>644</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.351</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.865</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.865</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.216</v>
       </c>
       <c r="Y31" t="n">
         <v>5.081</v>
@@ -5340,16 +5340,16 @@
         <v>37</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="Y32" t="n">
         <v>0.429</v>
@@ -5505,16 +5505,16 @@
         <v>314</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>0.233</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y33" t="n">
         <v>1.133</v>
@@ -5670,16 +5670,16 @@
         <v>594</v>
       </c>
       <c r="U34" t="n">
-        <v>0.111</v>
+        <v>2.389</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.444</v>
       </c>
       <c r="Y34" t="n">
         <v>6.972</v>
@@ -5841,10 +5841,10 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="Y35" t="n">
         <v>0.067</v>
@@ -6000,16 +6000,16 @@
         <v>123</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.233</v>
       </c>
       <c r="Y36" t="n">
         <v>1.533</v>
@@ -6165,16 +6165,16 @@
         <v>139</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.083</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.917</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="Y37" t="n">
         <v>3.833</v>
@@ -6330,16 +6330,16 @@
         <v>302</v>
       </c>
       <c r="U38" t="n">
-        <v>0.083</v>
+        <v>0.778</v>
       </c>
       <c r="V38" t="n">
-        <v>0.139</v>
+        <v>1.472</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.139</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="Y38" t="n">
         <v>1.667</v>
@@ -6495,16 +6495,16 @@
         <v>75</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>0.483</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="Y39" t="n">
         <v>0.759</v>
@@ -6660,16 +6660,16 @@
         <v>173</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.871</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="Y40" t="n">
         <v>1.839</v>
@@ -6825,16 +6825,16 @@
         <v>291</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1</v>
+        <v>0.733</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.433</v>
       </c>
       <c r="Y41" t="n">
         <v>3.133</v>
@@ -6990,10 +6990,10 @@
         <v>59</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.182</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>23</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -7320,16 +7320,16 @@
         <v>346</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08599999999999999</v>
+        <v>1.429</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.143</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>0.629</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="Y44" t="n">
         <v>1.743</v>
@@ -7485,16 +7485,16 @@
         <v>185</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.263</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="Y45" t="n">
         <v>1.816</v>
@@ -7815,16 +7815,16 @@
         <v>3565</v>
       </c>
       <c r="U47" t="n">
-        <v>0.342</v>
+        <v>8.553000000000001</v>
       </c>
       <c r="V47" t="n">
-        <v>0.132</v>
+        <v>10.658</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>8.446999999999999</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>5.263</v>
       </c>
       <c r="Y47" t="n">
         <v>26.895</v>
@@ -7980,16 +7980,16 @@
         <v>3626</v>
       </c>
       <c r="U48" t="n">
-        <v>0.211</v>
+        <v>9.5</v>
       </c>
       <c r="V48" t="n">
-        <v>0.368</v>
+        <v>10.737</v>
       </c>
       <c r="W48" t="n">
-        <v>0.158</v>
+        <v>9.053000000000001</v>
       </c>
       <c r="X48" t="n">
-        <v>0.079</v>
+        <v>5.421</v>
       </c>
       <c r="Y48" t="n">
         <v>29.579</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
@@ -683,13 +683,13 @@
         <v>480</v>
       </c>
       <c r="N2" t="n">
-        <v>1022</v>
+        <v>445</v>
       </c>
       <c r="O2" t="n">
-        <v>1242</v>
+        <v>665</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5303159692570453</v>
+        <v>0.2839453458582408</v>
       </c>
       <c r="Q2" t="n">
         <v>236</v>
@@ -710,25 +710,25 @@
         <v>0.06148590947907771</v>
       </c>
       <c r="W2" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="X2" t="n">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05081127241673783</v>
+        <v>0.06105892399658411</v>
       </c>
       <c r="Z2" t="n">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="AA2" t="n">
-        <v>871</v>
+        <v>847</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3719043552519214</v>
+        <v>0.3616567036720751</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.822866344605475</v>
+        <v>0.6691729323308271</v>
       </c>
       <c r="AD2" t="n">
         <v>0.434622467771639</v>
@@ -737,13 +737,13 @@
         <v>0.3611111111111111</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4033613445378151</v>
+        <v>0.4265734265734266</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3547646383467279</v>
+        <v>0.3494687131050768</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.64573268921095</v>
+        <v>1.338345864661654</v>
       </c>
       <c r="AI2" t="n">
         <v>0.7222222222222222</v>
@@ -813,13 +813,13 @@
         <v>12.63157894736842</v>
       </c>
       <c r="N3" t="n">
-        <v>26.89473684210526</v>
+        <v>11.71052631578947</v>
       </c>
       <c r="O3" t="n">
-        <v>32.68421052631579</v>
+        <v>17.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5303159692570452</v>
+        <v>0.2839453458582408</v>
       </c>
       <c r="Q3" t="n">
         <v>6.210526315789473</v>
@@ -840,25 +840,25 @@
         <v>0.06148590947907771</v>
       </c>
       <c r="W3" t="n">
-        <v>1.263157894736842</v>
+        <v>1.605263157894737</v>
       </c>
       <c r="X3" t="n">
-        <v>3.131578947368421</v>
+        <v>3.763157894736842</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05081127241673783</v>
+        <v>0.06105892399658411</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.131578947368421</v>
+        <v>7.789473684210527</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.92105263157895</v>
+        <v>22.28947368421053</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3719043552519214</v>
+        <v>0.3616567036720751</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8228663446054751</v>
+        <v>0.6691729323308271</v>
       </c>
       <c r="AD3" t="n">
         <v>0.434622467771639</v>
@@ -867,13 +867,13 @@
         <v>0.3611111111111112</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4033613445378151</v>
+        <v>0.4265734265734266</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3547646383467279</v>
+        <v>0.3494687131050767</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.64573268921095</v>
+        <v>1.338345864661654</v>
       </c>
       <c r="AI3" t="n">
         <v>0.7222222222222223</v>
@@ -943,13 +943,13 @@
         <v>398</v>
       </c>
       <c r="N4" t="n">
-        <v>1124</v>
+        <v>471</v>
       </c>
       <c r="O4" t="n">
-        <v>1376</v>
+        <v>723</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5752508361204013</v>
+        <v>0.302257525083612</v>
       </c>
       <c r="Q4" t="n">
         <v>233</v>
@@ -970,25 +970,25 @@
         <v>0.06020066889632107</v>
       </c>
       <c r="W4" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="X4" t="n">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05225752508361204</v>
+        <v>0.06229096989966555</v>
       </c>
       <c r="Z4" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AA4" t="n">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3277591973244147</v>
+        <v>0.3177257525083612</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8168604651162791</v>
+        <v>0.6514522821576764</v>
       </c>
       <c r="AD4" t="n">
         <v>0.3782467532467532</v>
@@ -997,13 +997,13 @@
         <v>0.4305555555555556</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.368</v>
+        <v>0.3758389261744967</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3137755102040816</v>
+        <v>0.3105263157894737</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.633720930232558</v>
+        <v>1.302904564315353</v>
       </c>
       <c r="AI4" t="n">
         <v>0.8611111111111112</v>
@@ -1073,13 +1073,13 @@
         <v>10.47368421052632</v>
       </c>
       <c r="N5" t="n">
-        <v>29.57894736842105</v>
+        <v>12.39473684210526</v>
       </c>
       <c r="O5" t="n">
-        <v>36.21052631578947</v>
+        <v>19.02631578947368</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5752508361204013</v>
+        <v>0.302257525083612</v>
       </c>
       <c r="Q5" t="n">
         <v>6.131578947368421</v>
@@ -1100,25 +1100,25 @@
         <v>0.06020066889632107</v>
       </c>
       <c r="W5" t="n">
-        <v>1.210526315789474</v>
+        <v>1.473684210526316</v>
       </c>
       <c r="X5" t="n">
-        <v>3.289473684210526</v>
+        <v>3.921052631578947</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05225752508361204</v>
+        <v>0.06229096989966555</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.473684210526316</v>
+        <v>6.210526315789473</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.63157894736842</v>
+        <v>20</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3277591973244147</v>
+        <v>0.3177257525083612</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8168604651162791</v>
+        <v>0.6514522821576764</v>
       </c>
       <c r="AD5" t="n">
         <v>0.3782467532467533</v>
@@ -1127,13 +1127,13 @@
         <v>0.4305555555555556</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.368</v>
+        <v>0.3758389261744966</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3137755102040816</v>
+        <v>0.3105263157894737</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.633720930232558</v>
+        <v>1.302904564315353</v>
       </c>
       <c r="AI5" t="n">
         <v>0.8611111111111112</v>
@@ -1498,13 +1498,13 @@
         <v>4</v>
       </c>
       <c r="Y8" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Z8" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.784</v>
+        <v>0.667</v>
       </c>
       <c r="AB8" t="n">
         <v>1</v>
@@ -1663,13 +1663,13 @@
         <v>6</v>
       </c>
       <c r="Y9" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.545</v>
       </c>
       <c r="AB9" t="n">
         <v>4</v>
@@ -1828,13 +1828,13 @@
         <v>45</v>
       </c>
       <c r="Y10" t="n">
-        <v>188</v>
+        <v>63</v>
       </c>
       <c r="Z10" t="n">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.874</v>
+        <v>0.7</v>
       </c>
       <c r="AB10" t="n">
         <v>65</v>
@@ -1858,19 +1858,19 @@
         <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AK10" t="n">
         <v>30</v>
       </c>
       <c r="AL10" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.278</v>
+        <v>0.283</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -1993,10 +1993,10 @@
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
         <v>1</v>
@@ -2020,22 +2020,22 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.458</v>
+        <v>0.435</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         <v>6</v>
       </c>
       <c r="Y12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Z12" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="AB12" t="n">
         <v>7</v>
@@ -2185,22 +2185,22 @@
         <v>0.417</v>
       </c>
       <c r="AH12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="AK12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AL12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.403</v>
+        <v>0.387</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -2323,13 +2323,13 @@
         <v>52</v>
       </c>
       <c r="Y13" t="n">
-        <v>251</v>
+        <v>129</v>
       </c>
       <c r="Z13" t="n">
-        <v>319</v>
+        <v>197</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.787</v>
+        <v>0.655</v>
       </c>
       <c r="AB13" t="n">
         <v>37</v>
@@ -2350,22 +2350,22 @@
         <v>0.231</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.286</v>
+        <v>0.294</v>
       </c>
       <c r="AK13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AL13" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.288</v>
+        <v>0.287</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
@@ -2488,13 +2488,13 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2653,13 +2653,13 @@
         <v>7</v>
       </c>
       <c r="Y15" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="Z15" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.821</v>
+        <v>0.722</v>
       </c>
       <c r="AB15" t="n">
         <v>6</v>
@@ -2680,22 +2680,22 @@
         <v>0.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AK15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.342</v>
+        <v>0.324</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         <v>8</v>
       </c>
       <c r="Y16" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.92</v>
+        <v>0.778</v>
       </c>
       <c r="AB16" t="n">
         <v>10</v>
@@ -2983,13 +2983,13 @@
         <v>20</v>
       </c>
       <c r="Y17" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.896</v>
+        <v>0.75</v>
       </c>
       <c r="AB17" t="n">
         <v>35</v>
@@ -3010,22 +3010,22 @@
         <v>0.269</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.421</v>
+        <v>0.476</v>
       </c>
       <c r="AK17" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AL17" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.396</v>
+        <v>0.389</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
@@ -3148,13 +3148,13 @@
         <v>7</v>
       </c>
       <c r="Y18" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.957</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AB18" t="n">
         <v>2</v>
@@ -3178,19 +3178,19 @@
         <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK18" t="n">
         <v>10</v>
       </c>
       <c r="AL18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.345</v>
+        <v>0.357</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
@@ -3313,13 +3313,13 @@
         <v>8</v>
       </c>
       <c r="Y19" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="Z19" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.792</v>
+        <v>0.531</v>
       </c>
       <c r="AB19" t="n">
         <v>7</v>
@@ -3340,22 +3340,22 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.222</v>
+        <v>0.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
@@ -3478,13 +3478,13 @@
         <v>13</v>
       </c>
       <c r="Y20" t="n">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="Z20" t="n">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.832</v>
+        <v>0.672</v>
       </c>
       <c r="AB20" t="n">
         <v>17</v>
@@ -3505,22 +3505,22 @@
         <v>0.667</v>
       </c>
       <c r="AH20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.125</v>
+        <v>0.333</v>
       </c>
       <c r="AK20" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.304</v>
+        <v>0.284</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
@@ -3643,13 +3643,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="Z21" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.829</v>
+        <v>0.739</v>
       </c>
       <c r="AB21" t="n">
         <v>3</v>
@@ -3808,10 +3808,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AA22" t="n">
         <v>1</v>
@@ -3973,13 +3973,13 @@
         <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.824</v>
+        <v>0.618</v>
       </c>
       <c r="AB23" t="n">
         <v>22</v>
@@ -4000,22 +4000,22 @@
         <v>0.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.533</v>
       </c>
       <c r="AK23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL23" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.459</v>
+        <v>0.464</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
@@ -4138,13 +4138,13 @@
         <v>7</v>
       </c>
       <c r="Y24" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="Z24" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.784</v>
+        <v>0.627</v>
       </c>
       <c r="AB24" t="n">
         <v>15</v>
@@ -4468,13 +4468,13 @@
         <v>200</v>
       </c>
       <c r="Y26" t="n">
-        <v>1022</v>
+        <v>445</v>
       </c>
       <c r="Z26" t="n">
-        <v>1242</v>
+        <v>665</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.823</v>
+        <v>0.669</v>
       </c>
       <c r="AB26" t="n">
         <v>236</v>
@@ -4495,22 +4495,22 @@
         <v>0.361</v>
       </c>
       <c r="AH26" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="AI26" t="n">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.403</v>
+        <v>0.427</v>
       </c>
       <c r="AK26" t="n">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="AL26" t="n">
-        <v>871</v>
+        <v>847</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.355</v>
+        <v>0.349</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>206</v>
       </c>
       <c r="Y27" t="n">
-        <v>1124</v>
+        <v>471</v>
       </c>
       <c r="Z27" t="n">
-        <v>1376</v>
+        <v>723</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.651</v>
       </c>
       <c r="AB27" t="n">
         <v>233</v>
@@ -4660,22 +4660,22 @@
         <v>0.431</v>
       </c>
       <c r="AH27" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="AI27" t="n">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.368</v>
+        <v>0.376</v>
       </c>
       <c r="AK27" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AL27" t="n">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.314</v>
+        <v>0.311</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
@@ -4857,13 +4857,13 @@
         <v>0.125</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.906</v>
+        <v>0.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.156</v>
+        <v>0.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.784</v>
+        <v>0.667</v>
       </c>
       <c r="AB29" t="n">
         <v>0.031</v>
@@ -5022,13 +5022,13 @@
         <v>0.188</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.188</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.844</v>
+        <v>0.344</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.545</v>
       </c>
       <c r="AB30" t="n">
         <v>0.125</v>
@@ -5187,13 +5187,13 @@
         <v>1.216</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.081</v>
+        <v>1.703</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.811</v>
+        <v>2.432</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.874</v>
+        <v>0.7</v>
       </c>
       <c r="AB31" t="n">
         <v>1.757</v>
@@ -5217,19 +5217,19 @@
         <v>0.054</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.189</v>
+        <v>0.243</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AK31" t="n">
         <v>0.8110000000000001</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.919</v>
+        <v>2.865</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.278</v>
+        <v>0.283</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
@@ -5352,10 +5352,10 @@
         <v>0.143</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.429</v>
+        <v>0.286</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.429</v>
+        <v>0.286</v>
       </c>
       <c r="AA32" t="n">
         <v>1</v>
@@ -5379,22 +5379,22 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.143</v>
+        <v>0.286</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.571</v>
+        <v>1.429</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.429</v>
+        <v>3.286</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.458</v>
+        <v>0.435</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>0.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.133</v>
+        <v>0.833</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.667</v>
+        <v>1.367</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="AB33" t="n">
         <v>0.233</v>
@@ -5544,22 +5544,22 @@
         <v>0.417</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.467</v>
+        <v>0.533</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.033</v>
+        <v>0.967</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.567</v>
+        <v>2.5</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.403</v>
+        <v>0.387</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -5682,13 +5682,13 @@
         <v>1.444</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.972</v>
+        <v>3.583</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.861000000000001</v>
+        <v>5.472</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.787</v>
+        <v>0.655</v>
       </c>
       <c r="AB34" t="n">
         <v>1.028</v>
@@ -5709,22 +5709,22 @@
         <v>0.231</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.111</v>
+        <v>0.139</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.389</v>
+        <v>0.472</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.286</v>
+        <v>0.294</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.944</v>
+        <v>0.917</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.278</v>
+        <v>3.194</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.288</v>
+        <v>0.287</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
@@ -5847,13 +5847,13 @@
         <v>0.067</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -6012,13 +6012,13 @@
         <v>0.233</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.533</v>
+        <v>0.867</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.867</v>
+        <v>1.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.821</v>
+        <v>0.722</v>
       </c>
       <c r="AB36" t="n">
         <v>0.2</v>
@@ -6039,22 +6039,22 @@
         <v>0.6</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.067</v>
+        <v>0.1</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.267</v>
+        <v>1.233</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.342</v>
+        <v>0.324</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
@@ -6177,13 +6177,13 @@
         <v>0.667</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.833</v>
+        <v>1.167</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.167</v>
+        <v>1.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.92</v>
+        <v>0.778</v>
       </c>
       <c r="AB37" t="n">
         <v>0.833</v>
@@ -6342,13 +6342,13 @@
         <v>0.556</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.667</v>
+        <v>0.583</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.861</v>
+        <v>0.778</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.896</v>
+        <v>0.75</v>
       </c>
       <c r="AB38" t="n">
         <v>0.972</v>
@@ -6369,22 +6369,22 @@
         <v>0.269</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.222</v>
+        <v>0.278</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.528</v>
+        <v>0.583</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.421</v>
+        <v>0.476</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.806</v>
+        <v>1.75</v>
       </c>
       <c r="AL38" t="n">
-        <v>4.556</v>
+        <v>4.5</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.396</v>
+        <v>0.389</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -6507,13 +6507,13 @@
         <v>0.241</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.759</v>
+        <v>0.517</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.793</v>
+        <v>0.552</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.957</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AB39" t="n">
         <v>0.06900000000000001</v>
@@ -6537,19 +6537,19 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.138</v>
+        <v>0.172</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK39" t="n">
         <v>0.345</v>
       </c>
       <c r="AL39" t="n">
-        <v>1</v>
+        <v>0.966</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.345</v>
+        <v>0.357</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
@@ -6672,13 +6672,13 @@
         <v>0.258</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.839</v>
+        <v>0.548</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.323</v>
+        <v>1.032</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.792</v>
+        <v>0.531</v>
       </c>
       <c r="AB40" t="n">
         <v>0.226</v>
@@ -6699,22 +6699,22 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.065</v>
+        <v>0.097</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.29</v>
+        <v>0.387</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.222</v>
+        <v>0.25</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.839</v>
+        <v>0.806</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.355</v>
+        <v>2.258</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
@@ -6837,13 +6837,13 @@
         <v>0.433</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.133</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.767</v>
+        <v>1.933</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.832</v>
+        <v>0.672</v>
       </c>
       <c r="AB41" t="n">
         <v>0.5669999999999999</v>
@@ -6864,22 +6864,22 @@
         <v>0.667</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.033</v>
+        <v>0.133</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.267</v>
+        <v>0.4</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.125</v>
+        <v>0.333</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="AL41" t="n">
-        <v>3.067</v>
+        <v>2.933</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.304</v>
+        <v>0.284</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
@@ -7002,13 +7002,13 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.636</v>
+        <v>1.545</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.182</v>
+        <v>2.091</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.829</v>
+        <v>0.739</v>
       </c>
       <c r="AB42" t="n">
         <v>0.273</v>
@@ -7167,10 +7167,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.833</v>
+        <v>0.167</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.833</v>
+        <v>0.167</v>
       </c>
       <c r="AA43" t="n">
         <v>1</v>
@@ -7332,13 +7332,13 @@
         <v>0.429</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.743</v>
+        <v>0.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.114</v>
+        <v>0.971</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.824</v>
+        <v>0.618</v>
       </c>
       <c r="AB44" t="n">
         <v>0.629</v>
@@ -7359,22 +7359,22 @@
         <v>0.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.4</v>
+        <v>0.457</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.714</v>
+        <v>0.857</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.533</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.971</v>
+        <v>0.914</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.114</v>
+        <v>1.971</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.459</v>
+        <v>0.464</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
@@ -7497,13 +7497,13 @@
         <v>0.184</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.816</v>
+        <v>0.842</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.316</v>
+        <v>1.342</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.784</v>
+        <v>0.627</v>
       </c>
       <c r="AB45" t="n">
         <v>0.395</v>
@@ -7827,13 +7827,13 @@
         <v>5.263</v>
       </c>
       <c r="Y47" t="n">
-        <v>26.895</v>
+        <v>11.711</v>
       </c>
       <c r="Z47" t="n">
-        <v>32.684</v>
+        <v>17.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.823</v>
+        <v>0.669</v>
       </c>
       <c r="AB47" t="n">
         <v>6.211</v>
@@ -7854,22 +7854,22 @@
         <v>0.361</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.263</v>
+        <v>1.605</v>
       </c>
       <c r="AI47" t="n">
-        <v>3.132</v>
+        <v>3.763</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.403</v>
+        <v>0.427</v>
       </c>
       <c r="AK47" t="n">
-        <v>8.132</v>
+        <v>7.789</v>
       </c>
       <c r="AL47" t="n">
-        <v>22.921</v>
+        <v>22.289</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.355</v>
+        <v>0.349</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
@@ -7992,13 +7992,13 @@
         <v>5.421</v>
       </c>
       <c r="Y48" t="n">
-        <v>29.579</v>
+        <v>12.395</v>
       </c>
       <c r="Z48" t="n">
-        <v>36.211</v>
+        <v>19.026</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.651</v>
       </c>
       <c r="AB48" t="n">
         <v>6.132</v>
@@ -8019,22 +8019,22 @@
         <v>0.431</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.211</v>
+        <v>1.474</v>
       </c>
       <c r="AI48" t="n">
-        <v>3.289</v>
+        <v>3.921</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.368</v>
+        <v>0.376</v>
       </c>
       <c r="AK48" t="n">
-        <v>6.474</v>
+        <v>6.211</v>
       </c>
       <c r="AL48" t="n">
-        <v>20.632</v>
+        <v>20</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.314</v>
+        <v>0.311</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
